--- a/ddl/REST_API_명세서_개선.xlsx
+++ b/ddl/REST_API_명세서_개선.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1740,6 +1740,40 @@
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>[신규 추가 엔드포인트] 상세 스펙 확인 필요. Auth: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>사용자 (내부)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>[신규] by-role 조회</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>/api/users/internal/by-role</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>[신규 추가 엔드포인트] 상세 스펙 확인 필요. Auth: -</t>
         </is>
@@ -1767,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4077,6 +4111,40 @@
       <c r="J46" s="5" t="inlineStr">
         <is>
           <t>[신규 추가 엔드포인트] 상세 스펙 확인 필요. Auth: hasRole('ADMIN')</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>바이어 (내부)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>[신규] by-client 조회</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>/api/buyers/internal/by-client/{clientId}</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>[신규 추가 엔드포인트] 상세 스펙 확인 필요. Auth: -</t>
         </is>
       </c>
     </row>
